--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,381 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121698052</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103627</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>680040</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6687633</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121697973</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98113</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>680043</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6687598</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121698145</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110250</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>679933</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6687560</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121697973</v>
+        <v>121698052</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>103627</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,25 +818,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,11 +849,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -862,10 +858,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680043</v>
+        <v>680040</v>
       </c>
       <c r="R3" t="n">
-        <v>6687598</v>
+        <v>6687633</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +893,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,7 +903,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121698145</v>
+        <v>121698178</v>
       </c>
       <c r="B4" t="n">
-        <v>110250</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +943,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,20 +969,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679933</v>
+        <v>680043</v>
       </c>
       <c r="R4" t="n">
-        <v>6687560</v>
+        <v>6687598</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,7 +1026,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1036,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,10 +1064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121698052</v>
+        <v>121698145</v>
       </c>
       <c r="B5" t="n">
-        <v>103627</v>
+        <v>110250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,16 +1080,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>219711</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1094,11 +1102,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1108,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680040</v>
+        <v>679933</v>
       </c>
       <c r="R5" t="n">
-        <v>6687633</v>
+        <v>6687560</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1147,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,7 +1157,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121698052</v>
+        <v>121698178</v>
       </c>
       <c r="B3" t="n">
-        <v>103627</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,25 +818,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,19 +849,27 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680040</v>
+        <v>680043</v>
       </c>
       <c r="R3" t="n">
-        <v>6687633</v>
+        <v>6687598</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +901,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -903,7 +911,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121698178</v>
+        <v>121698145</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>110250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,25 +951,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -969,32 +977,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680043</v>
+        <v>679933</v>
       </c>
       <c r="R4" t="n">
-        <v>6687598</v>
+        <v>6687560</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,7 +1032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121698145</v>
+        <v>121698052</v>
       </c>
       <c r="B5" t="n">
-        <v>110250</v>
+        <v>103627</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,16 +1076,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219711</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1102,7 +1098,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679933</v>
+        <v>680040</v>
       </c>
       <c r="R5" t="n">
-        <v>6687560</v>
+        <v>6687633</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121698178</v>
+        <v>121698052</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>103627</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,25 +818,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,27 +849,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680043</v>
+        <v>680040</v>
       </c>
       <c r="R3" t="n">
-        <v>6687598</v>
+        <v>6687633</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +893,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -911,7 +903,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121698145</v>
+        <v>121697973</v>
       </c>
       <c r="B4" t="n">
-        <v>110250</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,25 +943,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -977,8 +969,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679933</v>
+        <v>680043</v>
       </c>
       <c r="R4" t="n">
-        <v>6687560</v>
+        <v>6687598</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121698052</v>
+        <v>121698145</v>
       </c>
       <c r="B5" t="n">
-        <v>103627</v>
+        <v>110250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,16 +1076,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>219711</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1098,11 +1098,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1112,10 +1108,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680040</v>
+        <v>679933</v>
       </c>
       <c r="R5" t="n">
-        <v>6687633</v>
+        <v>6687560</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,7 +1143,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1157,7 +1153,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -931,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121697973</v>
+        <v>121698145</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>110250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,25 +943,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -969,16 +969,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -987,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680043</v>
+        <v>679933</v>
       </c>
       <c r="R4" t="n">
-        <v>6687598</v>
+        <v>6687560</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,10 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121698145</v>
+        <v>121698178</v>
       </c>
       <c r="B5" t="n">
-        <v>110250</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,25 +1064,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1098,20 +1090,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679933</v>
+        <v>680043</v>
       </c>
       <c r="R5" t="n">
-        <v>6687560</v>
+        <v>6687598</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1147,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,7 +1157,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121698052</v>
+        <v>121698145</v>
       </c>
       <c r="B3" t="n">
-        <v>103627</v>
+        <v>110250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -844,11 +844,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -858,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680040</v>
+        <v>679933</v>
       </c>
       <c r="R3" t="n">
-        <v>6687633</v>
+        <v>6687560</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -903,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121698145</v>
+        <v>121698052</v>
       </c>
       <c r="B4" t="n">
-        <v>110250</v>
+        <v>103627</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,16 +943,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219711</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -969,7 +965,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679933</v>
+        <v>680040</v>
       </c>
       <c r="R4" t="n">
-        <v>6687560</v>
+        <v>6687633</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121698178</v>
+        <v>121697973</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1101,11 +1101,7 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrskedika, Upl</t>
@@ -1147,7 +1143,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1157,7 +1153,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1052,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121697973</v>
+        <v>121983422</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1095,11 +1095,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1114,7 +1110,7 @@
         <v>6687598</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1143,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,7 +1149,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,6 +1174,618 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121983658</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98092</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>680047</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6687646</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121983824</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98031</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>680040</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6687633</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121983805</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98092</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>680040</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6687633</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121983708</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98136</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>680047</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6687646</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121983601</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90260</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>233196</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramaria rufescens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Corner</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>680055</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6687617</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121698145</v>
+        <v>121983422</v>
       </c>
       <c r="B3" t="n">
-        <v>110250</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,25 +818,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -844,7 +844,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -854,13 +858,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679933</v>
+        <v>680043</v>
       </c>
       <c r="R3" t="n">
-        <v>6687560</v>
+        <v>6687598</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,7 +893,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +903,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121698052</v>
+        <v>121698145</v>
       </c>
       <c r="B4" t="n">
-        <v>103627</v>
+        <v>110250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,16 +947,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>219711</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -965,11 +969,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680040</v>
+        <v>679933</v>
       </c>
       <c r="R4" t="n">
-        <v>6687633</v>
+        <v>6687560</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,10 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121983422</v>
+        <v>121698052</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>103627</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,25 +1064,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680043</v>
+        <v>680040</v>
       </c>
       <c r="R5" t="n">
-        <v>6687598</v>
+        <v>6687633</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121983658</v>
+        <v>121983601</v>
       </c>
       <c r="B6" t="n">
-        <v>98092</v>
+        <v>90260</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,35 +1189,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223609</v>
+        <v>233196</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Fjällfotad fingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Ramaria rufescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Corner</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1225,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680047</v>
+        <v>680055</v>
       </c>
       <c r="R6" t="n">
-        <v>6687646</v>
+        <v>6687617</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1263,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1270,7 +1273,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121983824</v>
+        <v>121983658</v>
       </c>
       <c r="B7" t="n">
-        <v>98031</v>
+        <v>98092</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,29 +1317,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223591</v>
+        <v>223609</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1346,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680040</v>
+        <v>680047</v>
       </c>
       <c r="R7" t="n">
-        <v>6687633</v>
+        <v>6687646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1391,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1540,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121983708</v>
+        <v>121983824</v>
       </c>
       <c r="B9" t="n">
-        <v>98136</v>
+        <v>98031</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1556,33 +1559,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1592,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680047</v>
+        <v>680040</v>
       </c>
       <c r="R9" t="n">
-        <v>6687646</v>
+        <v>6687633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1627,7 +1626,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1637,7 +1636,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1665,10 +1664,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121983601</v>
+        <v>121983708</v>
       </c>
       <c r="B10" t="n">
-        <v>90260</v>
+        <v>98136</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1677,38 +1676,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>233196</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Corner</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680055</v>
+        <v>680047</v>
       </c>
       <c r="R10" t="n">
-        <v>6687617</v>
+        <v>6687646</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121983422</v>
+        <v>121698145</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>110268</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,25 +818,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -844,11 +844,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -858,13 +854,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680043</v>
+        <v>679933</v>
       </c>
       <c r="R3" t="n">
-        <v>6687598</v>
+        <v>6687560</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -903,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121698145</v>
+        <v>121983422</v>
       </c>
       <c r="B4" t="n">
-        <v>110250</v>
+        <v>98131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -969,7 +965,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -979,13 +979,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679933</v>
+        <v>680043</v>
       </c>
       <c r="R4" t="n">
-        <v>6687560</v>
+        <v>6687598</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,7 +1055,7 @@
         <v>121698052</v>
       </c>
       <c r="B5" t="n">
-        <v>103627</v>
+        <v>103645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>121983601</v>
       </c>
       <c r="B6" t="n">
-        <v>90260</v>
+        <v>90274</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121983658</v>
+        <v>121983805</v>
       </c>
       <c r="B7" t="n">
-        <v>98092</v>
+        <v>98110</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680047</v>
+        <v>680040</v>
       </c>
       <c r="R7" t="n">
-        <v>6687646</v>
+        <v>6687633</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121983805</v>
+        <v>121983708</v>
       </c>
       <c r="B8" t="n">
-        <v>98092</v>
+        <v>98154</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,22 +1438,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223609</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1470,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680040</v>
+        <v>680047</v>
       </c>
       <c r="R8" t="n">
-        <v>6687633</v>
+        <v>6687646</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,7 +1550,7 @@
         <v>121983824</v>
       </c>
       <c r="B9" t="n">
-        <v>98031</v>
+        <v>98049</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1664,10 +1668,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121983708</v>
+        <v>121983658</v>
       </c>
       <c r="B10" t="n">
-        <v>98136</v>
+        <v>98110</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1680,26 +1684,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>223609</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>121698145</v>
       </c>
       <c r="B3" t="n">
-        <v>110268</v>
+        <v>110270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121983422</v>
+        <v>121698052</v>
       </c>
       <c r="B4" t="n">
-        <v>98131</v>
+        <v>103647</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -979,13 +979,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680043</v>
+        <v>680040</v>
       </c>
       <c r="R4" t="n">
-        <v>6687598</v>
+        <v>6687633</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,10 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121698052</v>
+        <v>121983422</v>
       </c>
       <c r="B5" t="n">
-        <v>103645</v>
+        <v>98133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,25 +1064,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680040</v>
+        <v>680043</v>
       </c>
       <c r="R5" t="n">
-        <v>6687633</v>
+        <v>6687598</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121983601</v>
+        <v>121983658</v>
       </c>
       <c r="B6" t="n">
-        <v>90274</v>
+        <v>98112</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,38 +1189,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>233196</v>
+        <v>223609</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Corner</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1228,10 +1225,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680055</v>
+        <v>680047</v>
       </c>
       <c r="R6" t="n">
-        <v>6687617</v>
+        <v>6687646</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1263,7 +1260,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1273,7 +1270,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,10 +1298,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121983805</v>
+        <v>121983824</v>
       </c>
       <c r="B7" t="n">
-        <v>98110</v>
+        <v>98051</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,29 +1314,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223609</v>
+        <v>223591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1384,7 +1381,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1391,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,7 +1422,7 @@
         <v>121983708</v>
       </c>
       <c r="B8" t="n">
-        <v>98154</v>
+        <v>98156</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1547,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121983824</v>
+        <v>121983601</v>
       </c>
       <c r="B9" t="n">
-        <v>98049</v>
+        <v>90276</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,25 +1556,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223591</v>
+        <v>233196</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fjällfotad fingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Ramaria rufescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Schaeff.) Corner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1585,9 +1582,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680040</v>
+        <v>680055</v>
       </c>
       <c r="R9" t="n">
-        <v>6687633</v>
+        <v>6687617</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1668,10 +1668,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121983658</v>
+        <v>121983805</v>
       </c>
       <c r="B10" t="n">
-        <v>98110</v>
+        <v>98112</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680047</v>
+        <v>680040</v>
       </c>
       <c r="R10" t="n">
-        <v>6687646</v>
+        <v>6687633</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121983658</v>
+        <v>121983824</v>
       </c>
       <c r="B6" t="n">
-        <v>98154</v>
+        <v>98093</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,29 +1193,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223609</v>
+        <v>223591</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680047</v>
+        <v>680040</v>
       </c>
       <c r="R6" t="n">
-        <v>6687646</v>
+        <v>6687633</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,10 +1298,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121983601</v>
+        <v>121983805</v>
       </c>
       <c r="B7" t="n">
-        <v>90311</v>
+        <v>98154</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,38 +1310,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>233196</v>
+        <v>223609</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Corner</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1349,10 +1346,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680055</v>
+        <v>680040</v>
       </c>
       <c r="R7" t="n">
-        <v>6687617</v>
+        <v>6687633</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1422,10 +1419,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121983708</v>
+        <v>121983601</v>
       </c>
       <c r="B8" t="n">
-        <v>98198</v>
+        <v>90311</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1434,39 +1431,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>233196</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fjällfotad fingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Ramaria rufescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Schaeff.) Corner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1474,10 +1470,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680047</v>
+        <v>680055</v>
       </c>
       <c r="R8" t="n">
-        <v>6687646</v>
+        <v>6687617</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1547,7 +1543,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121983805</v>
+        <v>121983658</v>
       </c>
       <c r="B9" t="n">
         <v>98154</v>
@@ -1578,7 +1574,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1595,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680040</v>
+        <v>680047</v>
       </c>
       <c r="R9" t="n">
-        <v>6687633</v>
+        <v>6687646</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1630,7 +1626,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1640,7 +1636,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1668,10 +1664,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121983824</v>
+        <v>121983708</v>
       </c>
       <c r="B10" t="n">
-        <v>98093</v>
+        <v>98198</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1684,29 +1680,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680040</v>
+        <v>680047</v>
       </c>
       <c r="R10" t="n">
-        <v>6687633</v>
+        <v>6687646</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>121983422</v>
       </c>
       <c r="B3" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>121983824</v>
       </c>
       <c r="B6" t="n">
-        <v>98093</v>
+        <v>98103</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121983805</v>
+        <v>121983708</v>
       </c>
       <c r="B7" t="n">
-        <v>98154</v>
+        <v>98208</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,22 +1314,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223609</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1346,10 +1350,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680040</v>
+        <v>680047</v>
       </c>
       <c r="R7" t="n">
-        <v>6687633</v>
+        <v>6687646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,10 +1423,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121983601</v>
+        <v>121983805</v>
       </c>
       <c r="B8" t="n">
-        <v>90311</v>
+        <v>98164</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,38 +1435,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>233196</v>
+        <v>223609</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Corner</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1470,10 +1471,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680055</v>
+        <v>680040</v>
       </c>
       <c r="R8" t="n">
-        <v>6687617</v>
+        <v>6687633</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,7 +1547,7 @@
         <v>121983658</v>
       </c>
       <c r="B9" t="n">
-        <v>98154</v>
+        <v>98164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1664,10 +1665,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121983708</v>
+        <v>121983601</v>
       </c>
       <c r="B10" t="n">
-        <v>98198</v>
+        <v>90321</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,39 +1677,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>233196</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fjällfotad fingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Ramaria rufescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Schaeff.) Corner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680047</v>
+        <v>680055</v>
       </c>
       <c r="R10" t="n">
-        <v>6687646</v>
+        <v>6687617</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121983824</v>
+        <v>121983658</v>
       </c>
       <c r="B6" t="n">
-        <v>98103</v>
+        <v>98164</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,29 +1193,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223591</v>
+        <v>223609</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680040</v>
+        <v>680047</v>
       </c>
       <c r="R6" t="n">
-        <v>6687633</v>
+        <v>6687646</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1544,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121983658</v>
+        <v>121983824</v>
       </c>
       <c r="B9" t="n">
-        <v>98164</v>
+        <v>98103</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,29 +1560,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223609</v>
+        <v>223591</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680047</v>
+        <v>680040</v>
       </c>
       <c r="R9" t="n">
-        <v>6687646</v>
+        <v>6687633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>121983422</v>
       </c>
       <c r="B3" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>121983658</v>
       </c>
       <c r="B6" t="n">
-        <v>98164</v>
+        <v>98176</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121983708</v>
+        <v>121983601</v>
       </c>
       <c r="B7" t="n">
-        <v>98208</v>
+        <v>90333</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,39 +1310,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>233196</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fjällfotad fingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Ramaria rufescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Schaeff.) Corner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1350,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680047</v>
+        <v>680055</v>
       </c>
       <c r="R7" t="n">
-        <v>6687646</v>
+        <v>6687617</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1423,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121983805</v>
+        <v>121983708</v>
       </c>
       <c r="B8" t="n">
-        <v>98164</v>
+        <v>98220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1439,22 +1438,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223609</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1471,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680040</v>
+        <v>680047</v>
       </c>
       <c r="R8" t="n">
-        <v>6687633</v>
+        <v>6687646</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1547,7 +1550,7 @@
         <v>121983824</v>
       </c>
       <c r="B9" t="n">
-        <v>98103</v>
+        <v>98115</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1665,10 +1668,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121983601</v>
+        <v>121983805</v>
       </c>
       <c r="B10" t="n">
-        <v>90321</v>
+        <v>98176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1677,38 +1680,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>233196</v>
+        <v>223609</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Corner</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680055</v>
+        <v>680040</v>
       </c>
       <c r="R10" t="n">
-        <v>6687617</v>
+        <v>6687633</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1792,7 +1792,7 @@
         <v>127106558</v>
       </c>
       <c r="B11" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>127106420</v>
       </c>
       <c r="B12" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>127106549</v>
       </c>
       <c r="B13" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>127106446</v>
       </c>
       <c r="B15" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1792,7 +1792,7 @@
         <v>127106558</v>
       </c>
       <c r="B11" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>127106420</v>
       </c>
       <c r="B12" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>127106549</v>
       </c>
       <c r="B13" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>127106446</v>
       </c>
       <c r="B15" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1792,7 +1792,7 @@
         <v>127106558</v>
       </c>
       <c r="B11" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>127106420</v>
       </c>
       <c r="B12" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>127106549</v>
       </c>
       <c r="B13" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>127106446</v>
       </c>
       <c r="B15" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1792,7 +1792,7 @@
         <v>127106558</v>
       </c>
       <c r="B11" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>127106420</v>
       </c>
       <c r="B12" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>127106549</v>
       </c>
       <c r="B13" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>127106271</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>127106446</v>
       </c>
       <c r="B15" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1792,7 +1792,7 @@
         <v>127106558</v>
       </c>
       <c r="B11" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>127106420</v>
       </c>
       <c r="B12" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>127106446</v>
       </c>
       <c r="B15" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1792,7 +1792,7 @@
         <v>127106558</v>
       </c>
       <c r="B11" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>127106420</v>
       </c>
       <c r="B12" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>127106549</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>127106271</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>127106446</v>
       </c>
       <c r="B15" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1792,7 +1792,7 @@
         <v>127106558</v>
       </c>
       <c r="B11" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>127106420</v>
       </c>
       <c r="B12" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>127106549</v>
       </c>
       <c r="B13" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>127106446</v>
       </c>
       <c r="B15" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1792,7 +1792,7 @@
         <v>127106558</v>
       </c>
       <c r="B11" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>127106420</v>
       </c>
       <c r="B12" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>127106549</v>
       </c>
       <c r="B13" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>127106271</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>127106446</v>
       </c>
       <c r="B15" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1792,7 +1792,7 @@
         <v>127106558</v>
       </c>
       <c r="B11" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>127106420</v>
       </c>
       <c r="B12" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>127106549</v>
       </c>
       <c r="B13" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>127106271</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>127106446</v>
       </c>
       <c r="B15" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1301,12 +1301,7 @@
         <v>121983601</v>
       </c>
       <c r="B7" t="n">
-        <v>90333</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91072</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1301,7 +1301,7 @@
         <v>121983601</v>
       </c>
       <c r="B7" t="n">
-        <v>91072</v>
+        <v>91073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1301,7 +1301,7 @@
         <v>121983601</v>
       </c>
       <c r="B7" t="n">
-        <v>91073</v>
+        <v>91076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1301,7 +1301,7 @@
         <v>121983601</v>
       </c>
       <c r="B7" t="n">
-        <v>91076</v>
+        <v>91078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1301,7 +1301,7 @@
         <v>121983601</v>
       </c>
       <c r="B7" t="n">
-        <v>91078</v>
+        <v>91082</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1301,7 +1301,7 @@
         <v>121983601</v>
       </c>
       <c r="B7" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1301,7 +1301,7 @@
         <v>121983601</v>
       </c>
       <c r="B7" t="n">
-        <v>91083</v>
+        <v>91086</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1301,7 +1301,7 @@
         <v>121983601</v>
       </c>
       <c r="B7" t="n">
-        <v>91086</v>
+        <v>91114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>127106271</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>57730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1301,7 +1301,7 @@
         <v>121983601</v>
       </c>
       <c r="B7" t="n">
-        <v>91114</v>
+        <v>91120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>127106271</v>
       </c>
       <c r="B14" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1301,7 +1301,7 @@
         <v>121983601</v>
       </c>
       <c r="B7" t="n">
-        <v>91120</v>
+        <v>91121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>127106271</v>
       </c>
       <c r="B14" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1301,7 +1301,7 @@
         <v>121983601</v>
       </c>
       <c r="B7" t="n">
-        <v>91121</v>
+        <v>91126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -2078,7 +2078,7 @@
         <v>127106271</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -2078,7 +2078,7 @@
         <v>127106271</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -1787,7 +1787,7 @@
         <v>127106558</v>
       </c>
       <c r="B11" t="n">
-        <v>98445</v>
+        <v>98414</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>127106420</v>
       </c>
       <c r="B12" t="n">
-        <v>98445</v>
+        <v>98414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>127106549</v>
       </c>
       <c r="B13" t="n">
-        <v>91369</v>
+        <v>91339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>127106446</v>
       </c>
       <c r="B15" t="n">
-        <v>98445</v>
+        <v>98414</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69551037</v>
+        <v>127106549</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Österön 2 km V om Norrskedika, Upl</t>
+          <t>Träsket, Träsket, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680057.4862429341</v>
+        <v>680039</v>
       </c>
       <c r="R2" t="n">
-        <v>6687614.115585978</v>
+        <v>6687666</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca. 20 ex. i lågörtvegetation under gran.</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,72 +756,61 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Äldre, örtrik barrskog.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121983422</v>
+        <v>121983394</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -858,13 +818,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680043</v>
+        <v>680006</v>
       </c>
       <c r="R3" t="n">
-        <v>6687598</v>
+        <v>6687665</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -903,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,65 +891,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121698052</v>
+        <v>127106271</v>
       </c>
       <c r="B4" t="n">
-        <v>103663</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrskedika, Upl</t>
+          <t>Träsket, Träsket, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680040</v>
+        <v>679981</v>
       </c>
       <c r="R4" t="n">
-        <v>6687633</v>
+        <v>6687512</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,22 +956,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>20:45</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>20:45</t>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,56 +975,50 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Susanne Åkesson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Susanne Åkesson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121698145</v>
+        <v>114467495</v>
       </c>
       <c r="B5" t="n">
-        <v>110286</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219711</v>
+        <v>100136</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1094,20 +1026,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrskedika, Upl</t>
+          <t>Norrskedika, Östhammar, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679933</v>
+        <v>679885</v>
       </c>
       <c r="R5" t="n">
-        <v>6687560</v>
+        <v>6687571</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,22 +1078,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>En adult lappuggla jagar längs åkerkanten och flög in i skogen. Möjlig häcklokal.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,7 +1107,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1177,45 +1125,40 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121983658</v>
+        <v>121698145</v>
       </c>
       <c r="B6" t="n">
-        <v>98176</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223609</v>
+        <v>219711</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1225,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680047</v>
+        <v>679933</v>
       </c>
       <c r="R6" t="n">
-        <v>6687646</v>
+        <v>6687560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1270,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,59 +1241,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121983601</v>
+        <v>127106420</v>
       </c>
       <c r="B7" t="n">
-        <v>91126</v>
+        <v>99096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>233196</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Corner</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrskedika, Upl</t>
+          <t>Träsket, Träsket, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680055</v>
+        <v>680053</v>
       </c>
       <c r="R7" t="n">
-        <v>6687617</v>
+        <v>6687557</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,22 +1306,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,34 +1320,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Susanne Åkesson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Susanne Åkesson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121983708</v>
+        <v>127106446</v>
       </c>
       <c r="B8" t="n">
-        <v>98220</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,49 +1349,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrskedika, Upl</t>
+          <t>Träsket, Träsket, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680047</v>
+        <v>680051</v>
       </c>
       <c r="R8" t="n">
-        <v>6687646</v>
+        <v>6687596</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,22 +1403,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,34 +1417,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Susanne Åkesson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Susanne Åkesson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121983824</v>
+        <v>127106558</v>
       </c>
       <c r="B9" t="n">
-        <v>98115</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,45 +1446,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrskedika, Upl</t>
+          <t>Träsket, Träsket, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680040</v>
+        <v>680039</v>
       </c>
       <c r="R9" t="n">
-        <v>6687633</v>
+        <v>6687665</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1620,22 +1500,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:45</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:45</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,34 +1514,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Susanne Åkesson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Susanne Åkesson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121983805</v>
+        <v>121983708</v>
       </c>
       <c r="B10" t="n">
-        <v>98176</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,22 +1543,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223609</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1711,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680040</v>
+        <v>680047</v>
       </c>
       <c r="R10" t="n">
-        <v>6687633</v>
+        <v>6687646</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1784,48 +1652,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127106558</v>
+        <v>121983422</v>
       </c>
       <c r="B11" t="n">
-        <v>98445</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Träsket, Träsket, Upl</t>
+          <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680039</v>
+        <v>680043</v>
       </c>
       <c r="R11" t="n">
-        <v>6687665</v>
+        <v>6687598</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1849,12 +1729,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,28 +1753,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Susanne Åkesson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Susanne Åkesson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127106420</v>
+        <v>121698052</v>
       </c>
       <c r="B12" t="n">
-        <v>98445</v>
+        <v>104628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,37 +1783,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Träsket, Träsket, Upl</t>
+          <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680053</v>
+        <v>680040</v>
       </c>
       <c r="R12" t="n">
-        <v>6687557</v>
+        <v>6687633</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1946,12 +1849,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,66 +1873,75 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Susanne Åkesson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Susanne Åkesson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127106549</v>
+        <v>121983824</v>
       </c>
       <c r="B13" t="n">
-        <v>91369</v>
+        <v>99036</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>223591</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Träsket, Träsket, Upl</t>
+          <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680039</v>
+        <v>680040</v>
       </c>
       <c r="R13" t="n">
-        <v>6687666</v>
+        <v>6687633</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2043,12 +1965,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,66 +1989,75 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Susanne Åkesson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Susanne Åkesson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127106271</v>
+        <v>121983658</v>
       </c>
       <c r="B14" t="n">
-        <v>57740</v>
+        <v>99097</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>223609</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Träsket, Träsket, Upl</t>
+          <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679981</v>
+        <v>680047</v>
       </c>
       <c r="R14" t="n">
-        <v>6687512</v>
+        <v>6687646</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2140,17 +2081,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,28 +2105,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Susanne Åkesson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Susanne Åkesson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127106446</v>
+        <v>121983805</v>
       </c>
       <c r="B15" t="n">
-        <v>98445</v>
+        <v>99097</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,37 +2135,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>223609</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Träsket, Träsket, Upl</t>
+          <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680051</v>
+        <v>680040</v>
       </c>
       <c r="R15" t="n">
-        <v>6687596</v>
+        <v>6687633</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2242,12 +2197,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,21 +2221,141 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Susanne Åkesson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Susanne Åkesson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121983601</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91433</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>233196</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fjällfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramaria rufescens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Corner</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>680055</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6687617</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1783-2023 artfynd.xlsx
+++ b/artfynd/A 1783-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127106549</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121983394</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127106271</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114467495</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121698145</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127106420</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,6 +1467,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127106446</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,6 +1569,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127106558</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121983708</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1769,6 +1819,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121983422</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121698052</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2005,6 +2065,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121983824</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2121,6 +2186,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121983658</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2237,6 +2307,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121983805</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2356,8 +2431,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121983601</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>